--- a/config/yunying/grid_walk_events.xlsx
+++ b/config/yunying/grid_walk_events.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>幸運ルーレット</t>
+          <t>幸运轮盘</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>マスに止まった時、ランダムな報酬を獲得できる。</t>
+          <t>停在格子时，可获得随机奖励。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>災難カード</t>
+          <t>灾难卡片</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>マスに止まった時、ペナルティを受ける。</t>
+          <t>停在格子上时，会受到惩罚。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>探検勲章+</t>
+          <t>探险勋章+</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>マスに止まった時、探検勲章+3を獲得できる。</t>
+          <t>停留在格子时，可获得探险勋章+3。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>探検勲章-</t>
+          <t>探索勋章</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>マスに止まった時、探検勲章-1を失う。</t>
+          <t>停在格子时，失去探险勋章-1。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ジャンプマス</t>
+          <t>跳跃</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>マスに止まった後、前に3マス進む事ができる。</t>
+          <t>停在格子后，可以前进3格。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ショップ</t>
+          <t>商店</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>マス上を経由または止まると商品を1回購入できる。</t>
+          <t>经过或停留在升上可以购买1次商品。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>マス上を経由または止まると豪華報酬を獲得できる。</t>
+          <t>经过或停在格子上就能获得豪华报酬。</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
